--- a/sales-analysis-project.xlsx
+++ b/sales-analysis-project.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30210"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30210"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8F4BDD5A-7297-4528-991A-9BAE9E1967EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F73EFF1C-32C9-40DE-9773-71B2979DD304}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pivot_analysis" sheetId="3" r:id="rId1"/>
@@ -13,11 +13,22 @@
     <sheet name="analysis" sheetId="2" r:id="rId3"/>
     <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="Slicer_Region">#N/A</definedName>
+  </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="165" r:id="rId5"/>
+    <pivotCache cacheId="703" r:id="rId5"/>
   </pivotCaches>
   <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
+      <x14:slicerCaches>
+        <x14:slicerCache r:id="rId6"/>
+      </x14:slicerCaches>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
+      <x14:workbookPr/>
+    </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
@@ -40,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="32">
   <si>
     <t>Sum of Sales</t>
   </si>
@@ -49,9 +60,6 @@
   </si>
   <si>
     <t>Category</t>
-  </si>
-  <si>
-    <t>EU</t>
   </si>
   <si>
     <t>US</t>
@@ -130,6 +138,9 @@
   </si>
   <si>
     <t>Tablet</t>
+  </si>
+  <si>
+    <t>EU</t>
   </si>
   <si>
     <t>Mouse</t>
@@ -239,7 +250,28 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -339,19 +371,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="5"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -467,7 +487,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>EU</c:v>
+                  <c:v>US</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -503,65 +523,6 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>140</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1300</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-A9AA-44B0-BEAE-9A8D9D0B6BF1}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Pivot_analysis!$C$3:$C$4</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>US</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent2"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:strRef>
-              <c:f>Pivot_analysis!$A$5:$A$7</c:f>
-              <c:strCache>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>Accessories</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Electronics</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Pivot_analysis!$C$5:$C$7</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
                   <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="1">
@@ -572,7 +533,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-A9AA-44B0-BEAE-9A8D9D0B6BF1}"/>
+              <c16:uniqueId val="{00000000-A9AA-44B0-BEAE-9A8D9D0B6BF1}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1446,7 +1407,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>EU</c:v>
+                  <c:v>US</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1482,65 +1443,6 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>140</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1300</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-0B39-4E1F-B72A-D5FD2D7592ED}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Pivot_analysis!$C$3:$C$4</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>US</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent2"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:strRef>
-              <c:f>Pivot_analysis!$A$5:$A$7</c:f>
-              <c:strCache>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>Accessories</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Electronics</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Pivot_analysis!$C$5:$C$7</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
                   <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="1">
@@ -1551,7 +1453,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-0B39-4E1F-B72A-D5FD2D7592ED}"/>
+              <c16:uniqueId val="{00000000-0B39-4E1F-B72A-D5FD2D7592ED}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2878,16 +2780,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>352425</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2910,6 +2812,83 @@
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>514350</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="3" name="Region">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF0771D9-5D41-96D2-7B24-DA63645CFB06}"/>
+                </a:ext>
+                <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+                  <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{FF06BB04-8240-1BDD-93E8-0E89F354834B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Region"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2305050" y="66675"/>
+              <a:ext cx="1828800" cy="1295400"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -2988,7 +2967,7 @@
   </cacheFields>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition/>
+      <x14:pivotCacheDefinition pivotCacheId="1106560592"/>
     </ext>
   </extLst>
 </pivotCacheDefinition>
@@ -3056,8 +3035,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7F47F1DF-0AFE-4794-AA89-1D33A00D7A99}" name="PivotTable1" cacheId="165" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="5">
-  <location ref="A3:D7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7F47F1DF-0AFE-4794-AA89-1D33A00D7A99}" name="PivotTable1" cacheId="703" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="5">
+  <location ref="A3:C7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField compact="0" outline="0" showAll="0"/>
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -3070,7 +3049,7 @@
     </pivotField>
     <pivotField axis="axisCol" compact="0" outline="0" showAll="0">
       <items count="3">
-        <item x="1"/>
+        <item h="1" x="1"/>
         <item x="0"/>
         <item t="default"/>
       </items>
@@ -3094,10 +3073,7 @@
   <colFields count="1">
     <field x="3"/>
   </colFields>
-  <colItems count="3">
-    <i>
-      <x/>
-    </i>
+  <colItems count="2">
     <i>
       <x v="1"/>
     </i>
@@ -3240,6 +3216,28 @@
     </ext>
   </extLst>
 </pivotTableDefinition>
+</file>
+
+<file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Region" xr10:uid="{1B1FA0D8-312F-4E4D-8AA9-1011CE05ECEE}" sourceName="Region">
+  <pivotTables>
+    <pivotTable tabId="3" name="PivotTable1"/>
+  </pivotTables>
+  <data>
+    <tabular pivotCacheId="1106560592">
+      <items count="2">
+        <i x="1"/>
+        <i x="0" s="1"/>
+      </items>
+    </tabular>
+  </data>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
+<slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
+  <slicer name="Region" xr10:uid="{061A7E99-0CCB-4E6C-B1F8-04C007436D58}" cache="Slicer_Region" caption="Region" rowHeight="228600"/>
+</slicers>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3539,16 +3537,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDC7831C-2283-4906-8A86-3731B024573B}">
-  <dimension ref="A3:D7"/>
+  <dimension ref="A3:C7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:3">
       <c r="A3" s="8" t="s">
         <v>0</v>
       </c>
@@ -3556,7 +3553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:3">
       <c r="A4" s="8" t="s">
         <v>2</v>
       </c>
@@ -3566,55 +3563,50 @@
       <c r="C4" t="s">
         <v>4</v>
       </c>
-      <c r="D4" t="s">
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
       <c r="B5" s="9">
-        <v>140</v>
+        <v>50</v>
       </c>
       <c r="C5" s="9">
         <v>50</v>
       </c>
-      <c r="D5" s="9">
-        <v>190</v>
-      </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" s="9">
-        <v>1300</v>
+        <v>800</v>
       </c>
       <c r="C6" s="9">
         <v>800</v>
       </c>
-      <c r="D6" s="9">
-        <v>2100</v>
-      </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7" s="9">
-        <v>1440</v>
+        <v>850</v>
       </c>
       <c r="C7" s="9">
         <v>850</v>
-      </c>
-      <c r="D7" s="9">
-        <v>2290</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
+      <x14:slicerList>
+        <x14:slicer r:id="rId3"/>
+      </x14:slicerList>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -3628,12 +3620,12 @@
   <sheetData>
     <row r="1" spans="2:3" ht="47.25">
       <c r="B1" s="10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="2:3">
       <c r="B4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4">
         <f>analysis!B8</f>
@@ -3642,7 +3634,7 @@
     </row>
     <row r="5" spans="2:3">
       <c r="B5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C5">
         <f>analysis!B9</f>
@@ -3651,7 +3643,7 @@
     </row>
     <row r="6" spans="2:3">
       <c r="B6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C6">
         <f>analysis!B10</f>
@@ -3660,7 +3652,7 @@
     </row>
     <row r="7" spans="2:3">
       <c r="B7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C7">
         <f>analysis!B11</f>
@@ -3669,7 +3661,7 @@
     </row>
     <row r="8" spans="2:3">
       <c r="B8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8">
         <f>analysis!B12</f>
@@ -3693,15 +3685,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" t="s">
         <v>14</v>
-      </c>
-      <c r="B1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="45.75">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B2" s="7">
         <f>SUMIFS(Sheet1!E:E,Sheet1!C:C,"Electronics",Sheet1!D:D,"EU")</f>
@@ -3710,7 +3702,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B3">
         <f>SUMIFS(Sheet1!E:E,Sheet1!C:C,"Accessories",Sheet1!D:D,"EU")</f>
@@ -3719,7 +3711,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B4">
         <f>SUMIF(Sheet1!D:D,"US",Sheet1!E:E)</f>
@@ -3728,7 +3720,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B5">
         <f>COUNTIFS(Sheet1!C:C,"Electronics",Sheet1!D:D,"EU")</f>
@@ -3737,7 +3729,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B6">
         <f>COUNTIF(Sheet1!D:D,"US")</f>
@@ -3746,7 +3738,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B7">
         <f>COUNTIF(Sheet1!C:C,"accessories")</f>
@@ -3755,7 +3747,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B8">
         <f>SUMIF(Sheet1!C:C,"Electronics",Sheet1!E:E)</f>
@@ -3764,7 +3756,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B9">
         <f>SUMIF(Sheet1!C:C,"Accessories",Sheet1!E:E)</f>
@@ -3773,7 +3765,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B10">
         <f>AVERAGE(Sheet1!E:E)</f>
@@ -3782,7 +3774,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11">
         <f>MAX(Sheet1!E:E)</f>
@@ -3791,7 +3783,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B12">
         <f>MIN(Sheet1!E:E)</f>
@@ -3816,10 +3808,10 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>2</v>
@@ -3828,7 +3820,7 @@
         <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -3836,13 +3828,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E2" s="5">
         <v>500</v>
@@ -3853,13 +3845,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E3" s="5">
         <v>300</v>
@@ -3870,13 +3862,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>29</v>
-      </c>
-      <c r="C4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>3</v>
       </c>
       <c r="E4" s="5">
         <v>400</v>
@@ -3890,10 +3882,10 @@
         <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E5" s="5">
         <v>50</v>
@@ -3907,10 +3899,10 @@
         <v>31</v>
       </c>
       <c r="C6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E6" s="5">
         <v>80</v>
@@ -3921,13 +3913,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E7" s="5">
         <v>350</v>
@@ -3938,13 +3930,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E8" s="5">
         <v>550</v>
@@ -3958,16 +3950,26 @@
         <v>30</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E9" s="5">
         <v>60</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="E2:E9">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
+      <formula>400</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E9">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
+      <formula>100</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>